--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_YORK_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_YORK_2015.xlsx
@@ -3937,7 +3937,7 @@
         <v>36</v>
       </c>
       <c r="D199">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="200">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
@@ -5233,7 +5233,7 @@
         <v>339</v>
       </c>
       <c r="D271">
-        <v>0.009048928275898887</v>
+        <v>0.009048928275898888</v>
       </c>
     </row>
     <row r="272">
@@ -6511,7 +6511,7 @@
         <v>36</v>
       </c>
       <c r="D342">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="343">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C731">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C732">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C794">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C918">
@@ -18625,7 +18625,7 @@
         <v>36</v>
       </c>
       <c r="D1015">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="1016">
@@ -19417,7 +19417,7 @@
         <v>36</v>
       </c>
       <c r="D1059">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="1060">
@@ -19957,7 +19957,7 @@
         <v>36</v>
       </c>
       <c r="D1089">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="1090">
@@ -20155,7 +20155,7 @@
         <v>339</v>
       </c>
       <c r="D1100">
-        <v>0.009048928275898887</v>
+        <v>0.009048928275898888</v>
       </c>
     </row>
     <row r="1101">
@@ -22927,7 +22927,7 @@
         <v>36</v>
       </c>
       <c r="D1254">
-        <v>0.0009609481354936871</v>
+        <v>0.0009609481354936872</v>
       </c>
     </row>
     <row r="1255">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1299">
